--- a/reports/pdf_rolling5_20260710.xlsx
+++ b/reports/pdf_rolling5_20260710.xlsx
@@ -574,7 +574,7 @@
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,389억      오늘 2026-07-10  vs  5일전 2026-07-03      매수 14종목  /  매도 15종목</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,448억      오늘 2026-07-10  vs  5일전 2026-07-03      매수 14종목  /  매도 15종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -670,7 +670,7 @@
         <v>109</v>
       </c>
       <c r="C6" s="11" t="n">
-        <v>939340200</v>
+        <v>877815150</v>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
@@ -691,7 +691,7 @@
         <v>-70</v>
       </c>
       <c r="I6" s="15" t="n">
-        <v>-1098742400</v>
+        <v>-1026776800</v>
       </c>
       <c r="J6" s="16" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
         <v>93</v>
       </c>
       <c r="C7" s="11" t="n">
-        <v>1038363600</v>
+        <v>970352700</v>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
@@ -735,7 +735,7 @@
         <v>-54</v>
       </c>
       <c r="I7" s="15" t="n">
-        <v>-875698560</v>
+        <v>-818341920</v>
       </c>
       <c r="J7" s="16" t="inlineStr">
         <is>
@@ -758,7 +758,7 @@
         <v>66</v>
       </c>
       <c r="C8" s="11" t="n">
-        <v>2443227600</v>
+        <v>2283200700</v>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>-52</v>
       </c>
       <c r="I8" s="15" t="n">
-        <v>-1567030400</v>
+        <v>-1464392800</v>
       </c>
       <c r="J8" s="16" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
         <v>60</v>
       </c>
       <c r="C9" s="11" t="n">
-        <v>4669872000</v>
+        <v>4364004000</v>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
@@ -823,7 +823,7 @@
         <v>-37</v>
       </c>
       <c r="I9" s="15" t="n">
-        <v>-1251369600</v>
+        <v>-1169407200</v>
       </c>
       <c r="J9" s="16" t="inlineStr">
         <is>
@@ -846,7 +846,7 @@
         <v>29</v>
       </c>
       <c r="C10" s="11" t="n">
-        <v>1468061200</v>
+        <v>1371905900</v>
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
@@ -867,7 +867,7 @@
         <v>-25</v>
       </c>
       <c r="I10" s="15" t="n">
-        <v>-3929500000</v>
+        <v>-3672125000</v>
       </c>
       <c r="J10" s="16" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>21</v>
       </c>
       <c r="C11" s="11" t="n">
-        <v>1971362400</v>
+        <v>1842241800</v>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>-23</v>
       </c>
       <c r="I11" s="15" t="n">
-        <v>-2615366800</v>
+        <v>-2444065100</v>
       </c>
       <c r="J11" s="16" t="inlineStr">
         <is>
@@ -934,7 +934,7 @@
         <v>20</v>
       </c>
       <c r="C12" s="11" t="n">
-        <v>1205408000</v>
+        <v>1126456000</v>
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
@@ -955,7 +955,7 @@
         <v>-22</v>
       </c>
       <c r="I12" s="15" t="n">
-        <v>-492461200</v>
+        <v>-460205900</v>
       </c>
       <c r="J12" s="16" t="inlineStr">
         <is>
@@ -978,7 +978,7 @@
         <v>16</v>
       </c>
       <c r="C13" s="11" t="n">
-        <v>1347628800</v>
+        <v>1259361600</v>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>-20</v>
       </c>
       <c r="I13" s="15" t="n">
-        <v>-904056000</v>
+        <v>-844842000</v>
       </c>
       <c r="J13" s="16" t="inlineStr">
         <is>
@@ -1022,7 +1022,7 @@
         <v>11</v>
       </c>
       <c r="C14" s="11" t="n">
-        <v>460266400</v>
+        <v>430119800</v>
       </c>
       <c r="D14" s="12" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
         <v>-19</v>
       </c>
       <c r="I14" s="15" t="n">
-        <v>-1377872400</v>
+        <v>-1287624300</v>
       </c>
       <c r="J14" s="16" t="inlineStr">
         <is>
@@ -1059,23 +1059,23 @@
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
         <is>
-          <t>와이지엔터테인먼트</t>
+          <t>동진쎄미켐</t>
         </is>
       </c>
       <c r="B15" s="11" t="n">
         <v>10</v>
       </c>
       <c r="C15" s="11" t="n">
-        <v>444982000</v>
+        <v>436603000</v>
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
-          <t>0.24%→0.35%</t>
+          <t>1.83%→1.86%</t>
         </is>
       </c>
       <c r="E15" s="13" t="inlineStr">
         <is>
-          <t>27→37</t>
+          <t>178→188</t>
         </is>
       </c>
       <c r="G15" s="14" t="inlineStr">
@@ -1087,7 +1087,7 @@
         <v>-17</v>
       </c>
       <c r="I15" s="15" t="n">
-        <v>-902972000</v>
+        <v>-843829000</v>
       </c>
       <c r="J15" s="16" t="inlineStr">
         <is>
@@ -1103,23 +1103,23 @@
     <row r="16">
       <c r="A16" s="10" t="inlineStr">
         <is>
-          <t>동진쎄미켐</t>
+          <t>와이지엔터테인먼트</t>
         </is>
       </c>
       <c r="B16" s="11" t="n">
         <v>10</v>
       </c>
       <c r="C16" s="11" t="n">
-        <v>467204000</v>
+        <v>415836500</v>
       </c>
       <c r="D16" s="12" t="inlineStr">
         <is>
-          <t>1.83%→1.86%</t>
+          <t>0.24%→0.35%</t>
         </is>
       </c>
       <c r="E16" s="13" t="inlineStr">
         <is>
-          <t>178→188</t>
+          <t>27→37</t>
         </is>
       </c>
       <c r="G16" s="14" t="inlineStr">
@@ -1131,7 +1131,7 @@
         <v>-16</v>
       </c>
       <c r="I16" s="15" t="n">
-        <v>-2639756800</v>
+        <v>-2466857600</v>
       </c>
       <c r="J16" s="16" t="inlineStr">
         <is>
@@ -1154,7 +1154,7 @@
         <v>8</v>
       </c>
       <c r="C17" s="11" t="n">
-        <v>1022428800</v>
+        <v>955461600</v>
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
@@ -1175,7 +1175,7 @@
         <v>-12</v>
       </c>
       <c r="I17" s="15" t="n">
-        <v>-457881600</v>
+        <v>-427891200</v>
       </c>
       <c r="J17" s="16" t="inlineStr">
         <is>
@@ -1198,7 +1198,7 @@
         <v>5</v>
       </c>
       <c r="C18" s="11" t="n">
-        <v>1626000000</v>
+        <v>1519500000</v>
       </c>
       <c r="D18" s="12" t="inlineStr">
         <is>
@@ -1219,7 +1219,7 @@
         <v>-10</v>
       </c>
       <c r="I18" s="15" t="n">
-        <v>-462868000</v>
+        <v>-432551000</v>
       </c>
       <c r="J18" s="16" t="inlineStr">
         <is>
@@ -1242,7 +1242,7 @@
         <v>5</v>
       </c>
       <c r="C19" s="11" t="n">
-        <v>1674780000</v>
+        <v>1565085000</v>
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>-6</v>
       </c>
       <c r="I19" s="15" t="n">
-        <v>-985356000</v>
+        <v>-920817000</v>
       </c>
       <c r="J19" s="16" t="inlineStr">
         <is>
@@ -1291,7 +1291,7 @@
         <v>-4</v>
       </c>
       <c r="I20" s="15" t="n">
-        <v>-512515200</v>
+        <v>-478946400</v>
       </c>
       <c r="J20" s="16" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
     <row r="22" ht="19" customHeight="1">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 4,354억      오늘 2026-07-10  vs  5일전 2026-07-03      매수 0종목  /  매도 0종목</t>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 4,303억      오늘 2026-07-10  vs  5일전 2026-07-03      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B22" s="4" t="n"/>
@@ -1331,7 +1331,7 @@
     <row r="25" ht="19" customHeight="1">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,513억      오늘 2026-07-10  vs  5일전 2026-07-03      매수 4종목  /  매도 5종목</t>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,562억      오늘 2026-07-10  vs  5일전 2026-07-03      매수 4종목  /  매도 5종목</t>
         </is>
       </c>
       <c r="B25" s="4" t="n"/>
@@ -1427,7 +1427,7 @@
         <v>201</v>
       </c>
       <c r="C28" s="11" t="n">
-        <v>6222397200</v>
+        <v>5330158200</v>
       </c>
       <c r="D28" s="12" t="inlineStr">
         <is>
@@ -1448,7 +1448,7 @@
         <v>-86</v>
       </c>
       <c r="I28" s="15" t="n">
-        <v>-7235162800</v>
+        <v>-6197701800</v>
       </c>
       <c r="J28" s="16" t="inlineStr">
         <is>
@@ -1471,7 +1471,7 @@
         <v>139</v>
       </c>
       <c r="C29" s="11" t="n">
-        <v>7781164400</v>
+        <v>6665411400</v>
       </c>
       <c r="D29" s="12" t="inlineStr">
         <is>
@@ -1492,7 +1492,7 @@
         <v>-81</v>
       </c>
       <c r="I29" s="15" t="n">
-        <v>-5047547400</v>
+        <v>-4323771900</v>
       </c>
       <c r="J29" s="16" t="inlineStr">
         <is>
@@ -1515,7 +1515,7 @@
         <v>35</v>
       </c>
       <c r="C30" s="11" t="n">
-        <v>8673630000</v>
+        <v>7429905000</v>
       </c>
       <c r="D30" s="12" t="inlineStr">
         <is>
@@ -1536,7 +1536,7 @@
         <v>-66</v>
       </c>
       <c r="I30" s="15" t="n">
-        <v>-7675140000</v>
+        <v>-6574590000</v>
       </c>
       <c r="J30" s="16" t="inlineStr">
         <is>
@@ -1559,7 +1559,7 @@
         <v>17</v>
       </c>
       <c r="C31" s="11" t="n">
-        <v>1611538800</v>
+        <v>1380457800</v>
       </c>
       <c r="D31" s="12" t="inlineStr">
         <is>
@@ -1580,7 +1580,7 @@
         <v>-58</v>
       </c>
       <c r="I31" s="15" t="n">
-        <v>-1637363200</v>
+        <v>-1402579200</v>
       </c>
       <c r="J31" s="16" t="inlineStr">
         <is>
@@ -1608,7 +1608,7 @@
         <v>-40</v>
       </c>
       <c r="I32" s="15" t="n">
-        <v>-4860120000</v>
+        <v>-4163220000</v>
       </c>
       <c r="J32" s="16" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
     <row r="34" ht="19" customHeight="1">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,581억      오늘 2026-07-10  vs  5일전 2026-07-03      매수 0종목  /  매도 0종목</t>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,548억      오늘 2026-07-10  vs  5일전 2026-07-03      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B34" s="4" t="n"/>
@@ -1648,7 +1648,7 @@
     <row r="37" ht="19" customHeight="1">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 324억      오늘 2026-07-10  vs  5일전 2026-07-03      매수 15종목  /  매도 15종목</t>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 329억      오늘 2026-07-10  vs  5일전 2026-07-03      매수 15종목  /  매도 15종목</t>
         </is>
       </c>
       <c r="B37" s="4" t="n"/>
@@ -1744,11 +1744,11 @@
         <v>121</v>
       </c>
       <c r="C40" s="11" t="n">
-        <v>84361200</v>
+        <v>87833900</v>
       </c>
       <c r="D40" s="12" t="inlineStr">
         <is>
-          <t>6.61%→6.85%</t>
+          <t>6.71%→6.95%</t>
         </is>
       </c>
       <c r="E40" s="13" t="inlineStr">
@@ -1765,11 +1765,11 @@
         <v>-318</v>
       </c>
       <c r="I40" s="15" t="n">
-        <v>-100837800</v>
+        <v>-100551600</v>
       </c>
       <c r="J40" s="16" t="inlineStr">
         <is>
-          <t>3.04%→2.71%</t>
+          <t>2.96%→2.64%</t>
         </is>
       </c>
       <c r="K40" s="13" t="inlineStr">
@@ -1788,11 +1788,11 @@
         <v>91</v>
       </c>
       <c r="C41" s="11" t="n">
-        <v>21479640</v>
+        <v>21541975</v>
       </c>
       <c r="D41" s="12" t="inlineStr">
         <is>
-          <t>0.38%→0.44%</t>
+          <t>0.37%→0.43%</t>
         </is>
       </c>
       <c r="E41" s="13" t="inlineStr">
@@ -1809,11 +1809,11 @@
         <v>-192</v>
       </c>
       <c r="I41" s="15" t="n">
-        <v>-103703040</v>
+        <v>-105590400</v>
       </c>
       <c r="J41" s="16" t="inlineStr">
         <is>
-          <t>0.64%→0.31%</t>
+          <t>0.63%→0.31%</t>
         </is>
       </c>
       <c r="K41" s="13" t="inlineStr">
@@ -1832,11 +1832,11 @@
         <v>37</v>
       </c>
       <c r="C42" s="11" t="n">
-        <v>96658800</v>
+        <v>109603250</v>
       </c>
       <c r="D42" s="12" t="inlineStr">
         <is>
-          <t>0.00%→0.30%</t>
+          <t>0.00%→0.33%</t>
         </is>
       </c>
       <c r="E42" s="13" t="inlineStr">
@@ -1846,23 +1846,23 @@
       </c>
       <c r="G42" s="14" t="inlineStr">
         <is>
-          <t>씨어스</t>
+          <t>서부T&amp;D</t>
         </is>
       </c>
       <c r="H42" s="15" t="n">
         <v>-36</v>
       </c>
       <c r="I42" s="15" t="n">
-        <v>-102211200</v>
+        <v>-31518000</v>
       </c>
       <c r="J42" s="16" t="inlineStr">
         <is>
-          <t>6.54%→6.19%</t>
+          <t>0.20%→0.10%</t>
         </is>
       </c>
       <c r="K42" s="13" t="inlineStr">
         <is>
-          <t>733→697</t>
+          <t>73→37</t>
         </is>
       </c>
     </row>
@@ -1876,11 +1876,11 @@
         <v>30</v>
       </c>
       <c r="C43" s="11" t="n">
-        <v>100800000</v>
+        <v>98430000</v>
       </c>
       <c r="D43" s="12" t="inlineStr">
         <is>
-          <t>2.22%→2.52%</t>
+          <t>2.11%→2.40%</t>
         </is>
       </c>
       <c r="E43" s="13" t="inlineStr">
@@ -1890,23 +1890,23 @@
       </c>
       <c r="G43" s="14" t="inlineStr">
         <is>
-          <t>서부T&amp;D</t>
+          <t>씨어스</t>
         </is>
       </c>
       <c r="H43" s="15" t="n">
         <v>-36</v>
       </c>
       <c r="I43" s="15" t="n">
-        <v>-31540320</v>
+        <v>-99450000</v>
       </c>
       <c r="J43" s="16" t="inlineStr">
         <is>
-          <t>0.20%→0.10%</t>
+          <t>6.20%→5.87%</t>
         </is>
       </c>
       <c r="K43" s="13" t="inlineStr">
         <is>
-          <t>73→37</t>
+          <t>733→697</t>
         </is>
       </c>
     </row>
@@ -1920,11 +1920,11 @@
         <v>16</v>
       </c>
       <c r="C44" s="11" t="n">
-        <v>182380800</v>
+        <v>197200000</v>
       </c>
       <c r="D44" s="12" t="inlineStr">
         <is>
-          <t>2.58%→3.14%</t>
+          <t>2.72%→3.30%</t>
         </is>
       </c>
       <c r="E44" s="13" t="inlineStr">
@@ -1934,23 +1934,23 @@
       </c>
       <c r="G44" s="14" t="inlineStr">
         <is>
-          <t>채비  (편출)</t>
+          <t>더핑크퐁컴퍼니</t>
         </is>
       </c>
       <c r="H44" s="15" t="n">
         <v>-34</v>
       </c>
       <c r="I44" s="15" t="n">
-        <v>-15907920</v>
+        <v>-31501000</v>
       </c>
       <c r="J44" s="16" t="inlineStr">
         <is>
-          <t>0.05%→0.00%</t>
+          <t>0.23%→0.14%</t>
         </is>
       </c>
       <c r="K44" s="13" t="inlineStr">
         <is>
-          <t>34→0</t>
+          <t>82→48</t>
         </is>
       </c>
     </row>
@@ -1964,11 +1964,11 @@
         <v>13</v>
       </c>
       <c r="C45" s="11" t="n">
-        <v>92820000</v>
+        <v>95693000</v>
       </c>
       <c r="D45" s="12" t="inlineStr">
         <is>
-          <t>3.36%→3.64%</t>
+          <t>3.38%→3.66%</t>
         </is>
       </c>
       <c r="E45" s="13" t="inlineStr">
@@ -1978,46 +1978,46 @@
       </c>
       <c r="G45" s="14" t="inlineStr">
         <is>
-          <t>더핑크퐁컴퍼니</t>
+          <t>채비  (편출)</t>
         </is>
       </c>
       <c r="H45" s="15" t="n">
         <v>-34</v>
       </c>
       <c r="I45" s="15" t="n">
-        <v>-29816640</v>
+        <v>-16010600</v>
       </c>
       <c r="J45" s="16" t="inlineStr">
         <is>
-          <t>0.23%→0.13%</t>
+          <t>0.05%→0.00%</t>
         </is>
       </c>
       <c r="K45" s="13" t="inlineStr">
         <is>
-          <t>82→48</t>
+          <t>34→0</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="10" t="inlineStr">
         <is>
-          <t>피에스케이</t>
+          <t>원익IPS</t>
         </is>
       </c>
       <c r="B46" s="11" t="n">
         <v>12</v>
       </c>
       <c r="C46" s="11" t="n">
-        <v>152611200</v>
+        <v>106998000</v>
       </c>
       <c r="D46" s="12" t="inlineStr">
         <is>
-          <t>2.40%→2.87%</t>
+          <t>2.32%→2.63%</t>
         </is>
       </c>
       <c r="E46" s="13" t="inlineStr">
         <is>
-          <t>60→72</t>
+          <t>85→97</t>
         </is>
       </c>
       <c r="G46" s="14" t="inlineStr">
@@ -2029,11 +2029,11 @@
         <v>-31</v>
       </c>
       <c r="I46" s="15" t="n">
-        <v>-46325160</v>
+        <v>-46165200</v>
       </c>
       <c r="J46" s="16" t="inlineStr">
         <is>
-          <t>0.35%→0.21%</t>
+          <t>0.34%→0.20%</t>
         </is>
       </c>
       <c r="K46" s="13" t="inlineStr">
@@ -2045,23 +2045,23 @@
     <row r="47">
       <c r="A47" s="10" t="inlineStr">
         <is>
-          <t>원익IPS</t>
+          <t>피에스케이</t>
         </is>
       </c>
       <c r="B47" s="11" t="n">
         <v>12</v>
       </c>
       <c r="C47" s="11" t="n">
-        <v>103521600</v>
+        <v>155244000</v>
       </c>
       <c r="D47" s="12" t="inlineStr">
         <is>
-          <t>2.30%→2.62%</t>
+          <t>2.38%→2.84%</t>
         </is>
       </c>
       <c r="E47" s="13" t="inlineStr">
         <is>
-          <t>85→97</t>
+          <t>60→72</t>
         </is>
       </c>
       <c r="G47" s="14" t="inlineStr">
@@ -2073,11 +2073,11 @@
         <v>-27</v>
       </c>
       <c r="I47" s="15" t="n">
-        <v>-68493600</v>
+        <v>-77571000</v>
       </c>
       <c r="J47" s="16" t="inlineStr">
         <is>
-          <t>0.22%→0.00%</t>
+          <t>0.24%→0.00%</t>
         </is>
       </c>
       <c r="K47" s="13" t="inlineStr">
@@ -2096,11 +2096,11 @@
         <v>10</v>
       </c>
       <c r="C48" s="11" t="n">
-        <v>55776000</v>
+        <v>64515000</v>
       </c>
       <c r="D48" s="12" t="inlineStr">
         <is>
-          <t>2.49%→2.65%</t>
+          <t>2.80%→2.99%</t>
         </is>
       </c>
       <c r="E48" s="13" t="inlineStr">
@@ -2117,11 +2117,11 @@
         <v>-16</v>
       </c>
       <c r="I48" s="15" t="n">
-        <v>-48384000</v>
+        <v>-48348000</v>
       </c>
       <c r="J48" s="16" t="inlineStr">
         <is>
-          <t>0.81%→0.65%</t>
+          <t>0.79%→0.64%</t>
         </is>
       </c>
       <c r="K48" s="13" t="inlineStr">
@@ -2140,11 +2140,11 @@
         <v>10</v>
       </c>
       <c r="C49" s="11" t="n">
-        <v>32130000</v>
+        <v>33405000</v>
       </c>
       <c r="D49" s="12" t="inlineStr">
         <is>
-          <t>1.15%→1.25%</t>
+          <t>1.17%→1.26%</t>
         </is>
       </c>
       <c r="E49" s="13" t="inlineStr">
@@ -2161,7 +2161,7 @@
         <v>-14</v>
       </c>
       <c r="I49" s="15" t="n">
-        <v>-35103600</v>
+        <v>-35759500</v>
       </c>
       <c r="J49" s="16" t="inlineStr">
         <is>
@@ -2177,23 +2177,23 @@
     <row r="50">
       <c r="A50" s="10" t="inlineStr">
         <is>
-          <t>대주전자재료</t>
+          <t>씨엠티엑스</t>
         </is>
       </c>
       <c r="B50" s="11" t="n">
         <v>6</v>
       </c>
       <c r="C50" s="11" t="n">
-        <v>37396800</v>
+        <v>38709000</v>
       </c>
       <c r="D50" s="12" t="inlineStr">
         <is>
-          <t>1.43%→1.54%</t>
+          <t>0.91%→1.02%</t>
         </is>
       </c>
       <c r="E50" s="13" t="inlineStr">
         <is>
-          <t>73→79</t>
+          <t>46→52</t>
         </is>
       </c>
       <c r="G50" s="14" t="inlineStr">
@@ -2205,11 +2205,11 @@
         <v>-14</v>
       </c>
       <c r="I50" s="15" t="n">
-        <v>-38572800</v>
+        <v>-40162500</v>
       </c>
       <c r="J50" s="16" t="inlineStr">
         <is>
-          <t>0.72%→0.59%</t>
+          <t>0.73%→0.60%</t>
         </is>
       </c>
       <c r="K50" s="13" t="inlineStr">
@@ -2221,23 +2221,23 @@
     <row r="51">
       <c r="A51" s="10" t="inlineStr">
         <is>
-          <t>씨엠티엑스</t>
+          <t>대주전자재료</t>
         </is>
       </c>
       <c r="B51" s="11" t="n">
         <v>6</v>
       </c>
       <c r="C51" s="11" t="n">
-        <v>34725600</v>
+        <v>38046000</v>
       </c>
       <c r="D51" s="12" t="inlineStr">
         <is>
-          <t>0.84%→0.94%</t>
+          <t>1.42%→1.53%</t>
         </is>
       </c>
       <c r="E51" s="13" t="inlineStr">
         <is>
-          <t>46→52</t>
+          <t>73→79</t>
         </is>
       </c>
       <c r="G51" s="14" t="inlineStr">
@@ -2249,11 +2249,11 @@
         <v>-13</v>
       </c>
       <c r="I51" s="15" t="n">
-        <v>-99372000</v>
+        <v>-100223500</v>
       </c>
       <c r="J51" s="16" t="inlineStr">
         <is>
-          <t>2.35%→2.03%</t>
+          <t>2.31%→2.00%</t>
         </is>
       </c>
       <c r="K51" s="13" t="inlineStr">
@@ -2272,11 +2272,11 @@
         <v>5</v>
       </c>
       <c r="C52" s="11" t="n">
-        <v>18312000</v>
+        <v>17722500</v>
       </c>
       <c r="D52" s="12" t="inlineStr">
         <is>
-          <t>7.24%→7.27%</t>
+          <t>6.83%→6.85%</t>
         </is>
       </c>
       <c r="E52" s="13" t="inlineStr">
@@ -2293,11 +2293,11 @@
         <v>-10</v>
       </c>
       <c r="I52" s="15" t="n">
-        <v>-69048000</v>
+        <v>-73610000</v>
       </c>
       <c r="J52" s="16" t="inlineStr">
         <is>
-          <t>1.04%→0.82%</t>
+          <t>1.08%→0.85%</t>
         </is>
       </c>
       <c r="K52" s="13" t="inlineStr">
@@ -2316,7 +2316,7 @@
         <v>5</v>
       </c>
       <c r="C53" s="11" t="n">
-        <v>33768000</v>
+        <v>36337500</v>
       </c>
       <c r="D53" s="12" t="inlineStr">
         <is>
@@ -2337,11 +2337,11 @@
         <v>-7</v>
       </c>
       <c r="I53" s="15" t="n">
-        <v>-68325600</v>
+        <v>-68544000</v>
       </c>
       <c r="J53" s="16" t="inlineStr">
         <is>
-          <t>3.28%→3.05%</t>
+          <t>3.21%→2.98%</t>
         </is>
       </c>
       <c r="K53" s="13" t="inlineStr">
@@ -2360,11 +2360,11 @@
         <v>3</v>
       </c>
       <c r="C54" s="11" t="n">
-        <v>54180000</v>
+        <v>57630000</v>
       </c>
       <c r="D54" s="12" t="inlineStr">
         <is>
-          <t>2.50%→2.66%</t>
+          <t>2.59%→2.75%</t>
         </is>
       </c>
       <c r="E54" s="13" t="inlineStr">
@@ -2381,11 +2381,11 @@
         <v>-3</v>
       </c>
       <c r="I54" s="15" t="n">
-        <v>-68166000</v>
+        <v>-73567500</v>
       </c>
       <c r="J54" s="16" t="inlineStr">
         <is>
-          <t>1.93%→1.71%</t>
+          <t>2.03%→1.79%</t>
         </is>
       </c>
       <c r="K54" s="13" t="inlineStr">
@@ -2397,7 +2397,7 @@
     <row r="56" ht="19" customHeight="1">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 571억      오늘 2026-07-10  vs  5일전 2026-07-03      매수 6종목  /  매도 4종목</t>
+          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 568억      오늘 2026-07-10  vs  5일전 2026-07-03      매수 6종목  /  매도 4종목</t>
         </is>
       </c>
       <c r="B56" s="4" t="n"/>

--- a/reports/pdf_rolling5_20260710.xlsx
+++ b/reports/pdf_rolling5_20260710.xlsx
@@ -1846,23 +1846,23 @@
       </c>
       <c r="G42" s="14" t="inlineStr">
         <is>
-          <t>서부T&amp;D</t>
+          <t>씨어스</t>
         </is>
       </c>
       <c r="H42" s="15" t="n">
         <v>-36</v>
       </c>
       <c r="I42" s="15" t="n">
-        <v>-31518000</v>
+        <v>-99450000</v>
       </c>
       <c r="J42" s="16" t="inlineStr">
         <is>
-          <t>0.20%→0.10%</t>
+          <t>6.20%→5.87%</t>
         </is>
       </c>
       <c r="K42" s="13" t="inlineStr">
         <is>
-          <t>73→37</t>
+          <t>733→697</t>
         </is>
       </c>
     </row>
@@ -1890,23 +1890,23 @@
       </c>
       <c r="G43" s="14" t="inlineStr">
         <is>
-          <t>씨어스</t>
+          <t>서부T&amp;D</t>
         </is>
       </c>
       <c r="H43" s="15" t="n">
         <v>-36</v>
       </c>
       <c r="I43" s="15" t="n">
-        <v>-99450000</v>
+        <v>-31518000</v>
       </c>
       <c r="J43" s="16" t="inlineStr">
         <is>
-          <t>6.20%→5.87%</t>
+          <t>0.20%→0.10%</t>
         </is>
       </c>
       <c r="K43" s="13" t="inlineStr">
         <is>
-          <t>733→697</t>
+          <t>73→37</t>
         </is>
       </c>
     </row>
@@ -1934,23 +1934,23 @@
       </c>
       <c r="G44" s="14" t="inlineStr">
         <is>
-          <t>더핑크퐁컴퍼니</t>
+          <t>채비  (편출)</t>
         </is>
       </c>
       <c r="H44" s="15" t="n">
         <v>-34</v>
       </c>
       <c r="I44" s="15" t="n">
-        <v>-31501000</v>
+        <v>-16010600</v>
       </c>
       <c r="J44" s="16" t="inlineStr">
         <is>
-          <t>0.23%→0.14%</t>
+          <t>0.05%→0.00%</t>
         </is>
       </c>
       <c r="K44" s="13" t="inlineStr">
         <is>
-          <t>82→48</t>
+          <t>34→0</t>
         </is>
       </c>
     </row>
@@ -1978,23 +1978,23 @@
       </c>
       <c r="G45" s="14" t="inlineStr">
         <is>
-          <t>채비  (편출)</t>
+          <t>더핑크퐁컴퍼니</t>
         </is>
       </c>
       <c r="H45" s="15" t="n">
         <v>-34</v>
       </c>
       <c r="I45" s="15" t="n">
-        <v>-16010600</v>
+        <v>-31501000</v>
       </c>
       <c r="J45" s="16" t="inlineStr">
         <is>
-          <t>0.05%→0.00%</t>
+          <t>0.23%→0.14%</t>
         </is>
       </c>
       <c r="K45" s="13" t="inlineStr">
         <is>
-          <t>34→0</t>
+          <t>82→48</t>
         </is>
       </c>
     </row>
@@ -2089,23 +2089,23 @@
     <row r="48">
       <c r="A48" s="10" t="inlineStr">
         <is>
-          <t>코미코</t>
+          <t>HPSP</t>
         </is>
       </c>
       <c r="B48" s="11" t="n">
         <v>10</v>
       </c>
       <c r="C48" s="11" t="n">
-        <v>64515000</v>
+        <v>33405000</v>
       </c>
       <c r="D48" s="12" t="inlineStr">
         <is>
-          <t>2.80%→2.99%</t>
+          <t>1.17%→1.26%</t>
         </is>
       </c>
       <c r="E48" s="13" t="inlineStr">
         <is>
-          <t>142→152</t>
+          <t>114→124</t>
         </is>
       </c>
       <c r="G48" s="14" t="inlineStr">
@@ -2133,111 +2133,111 @@
     <row r="49">
       <c r="A49" s="10" t="inlineStr">
         <is>
-          <t>HPSP</t>
+          <t>코미코</t>
         </is>
       </c>
       <c r="B49" s="11" t="n">
         <v>10</v>
       </c>
       <c r="C49" s="11" t="n">
-        <v>33405000</v>
+        <v>64515000</v>
       </c>
       <c r="D49" s="12" t="inlineStr">
         <is>
-          <t>1.17%→1.26%</t>
+          <t>2.80%→2.99%</t>
         </is>
       </c>
       <c r="E49" s="13" t="inlineStr">
         <is>
-          <t>114→124</t>
+          <t>142→152</t>
         </is>
       </c>
       <c r="G49" s="14" t="inlineStr">
         <is>
-          <t>하이록코리아</t>
+          <t>솔브레인홀딩스</t>
         </is>
       </c>
       <c r="H49" s="15" t="n">
         <v>-14</v>
       </c>
       <c r="I49" s="15" t="n">
-        <v>-35759500</v>
+        <v>-40162500</v>
       </c>
       <c r="J49" s="16" t="inlineStr">
         <is>
-          <t>0.21%→0.10%</t>
+          <t>0.73%→0.60%</t>
         </is>
       </c>
       <c r="K49" s="13" t="inlineStr">
         <is>
-          <t>27→13</t>
+          <t>83→69</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="10" t="inlineStr">
         <is>
-          <t>씨엠티엑스</t>
+          <t>대주전자재료</t>
         </is>
       </c>
       <c r="B50" s="11" t="n">
         <v>6</v>
       </c>
       <c r="C50" s="11" t="n">
-        <v>38709000</v>
+        <v>38046000</v>
       </c>
       <c r="D50" s="12" t="inlineStr">
         <is>
-          <t>0.91%→1.02%</t>
+          <t>1.42%→1.53%</t>
         </is>
       </c>
       <c r="E50" s="13" t="inlineStr">
         <is>
-          <t>46→52</t>
+          <t>73→79</t>
         </is>
       </c>
       <c r="G50" s="14" t="inlineStr">
         <is>
-          <t>솔브레인홀딩스</t>
+          <t>하이록코리아</t>
         </is>
       </c>
       <c r="H50" s="15" t="n">
         <v>-14</v>
       </c>
       <c r="I50" s="15" t="n">
-        <v>-40162500</v>
+        <v>-35759500</v>
       </c>
       <c r="J50" s="16" t="inlineStr">
         <is>
-          <t>0.73%→0.60%</t>
+          <t>0.21%→0.10%</t>
         </is>
       </c>
       <c r="K50" s="13" t="inlineStr">
         <is>
-          <t>83→69</t>
+          <t>27→13</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="10" t="inlineStr">
         <is>
-          <t>대주전자재료</t>
+          <t>씨엠티엑스</t>
         </is>
       </c>
       <c r="B51" s="11" t="n">
         <v>6</v>
       </c>
       <c r="C51" s="11" t="n">
-        <v>38046000</v>
+        <v>38709000</v>
       </c>
       <c r="D51" s="12" t="inlineStr">
         <is>
-          <t>1.42%→1.53%</t>
+          <t>0.91%→1.02%</t>
         </is>
       </c>
       <c r="E51" s="13" t="inlineStr">
         <is>
-          <t>73→79</t>
+          <t>46→52</t>
         </is>
       </c>
       <c r="G51" s="14" t="inlineStr">

--- a/reports/pdf_rolling5_20260710.xlsx
+++ b/reports/pdf_rolling5_20260710.xlsx
@@ -1846,23 +1846,23 @@
       </c>
       <c r="G42" s="14" t="inlineStr">
         <is>
-          <t>씨어스</t>
+          <t>서부T&amp;D</t>
         </is>
       </c>
       <c r="H42" s="15" t="n">
         <v>-36</v>
       </c>
       <c r="I42" s="15" t="n">
-        <v>-99450000</v>
+        <v>-31518000</v>
       </c>
       <c r="J42" s="16" t="inlineStr">
         <is>
-          <t>6.20%→5.87%</t>
+          <t>0.20%→0.10%</t>
         </is>
       </c>
       <c r="K42" s="13" t="inlineStr">
         <is>
-          <t>733→697</t>
+          <t>73→37</t>
         </is>
       </c>
     </row>
@@ -1890,23 +1890,23 @@
       </c>
       <c r="G43" s="14" t="inlineStr">
         <is>
-          <t>서부T&amp;D</t>
+          <t>씨어스</t>
         </is>
       </c>
       <c r="H43" s="15" t="n">
         <v>-36</v>
       </c>
       <c r="I43" s="15" t="n">
-        <v>-31518000</v>
+        <v>-99450000</v>
       </c>
       <c r="J43" s="16" t="inlineStr">
         <is>
-          <t>0.20%→0.10%</t>
+          <t>6.20%→5.87%</t>
         </is>
       </c>
       <c r="K43" s="13" t="inlineStr">
         <is>
-          <t>73→37</t>
+          <t>733→697</t>
         </is>
       </c>
     </row>
@@ -1934,23 +1934,23 @@
       </c>
       <c r="G44" s="14" t="inlineStr">
         <is>
-          <t>채비  (편출)</t>
+          <t>더핑크퐁컴퍼니</t>
         </is>
       </c>
       <c r="H44" s="15" t="n">
         <v>-34</v>
       </c>
       <c r="I44" s="15" t="n">
-        <v>-16010600</v>
+        <v>-31501000</v>
       </c>
       <c r="J44" s="16" t="inlineStr">
         <is>
-          <t>0.05%→0.00%</t>
+          <t>0.23%→0.14%</t>
         </is>
       </c>
       <c r="K44" s="13" t="inlineStr">
         <is>
-          <t>34→0</t>
+          <t>82→48</t>
         </is>
       </c>
     </row>
@@ -1978,23 +1978,23 @@
       </c>
       <c r="G45" s="14" t="inlineStr">
         <is>
-          <t>더핑크퐁컴퍼니</t>
+          <t>채비  (편출)</t>
         </is>
       </c>
       <c r="H45" s="15" t="n">
         <v>-34</v>
       </c>
       <c r="I45" s="15" t="n">
-        <v>-31501000</v>
+        <v>-16010600</v>
       </c>
       <c r="J45" s="16" t="inlineStr">
         <is>
-          <t>0.23%→0.14%</t>
+          <t>0.05%→0.00%</t>
         </is>
       </c>
       <c r="K45" s="13" t="inlineStr">
         <is>
-          <t>82→48</t>
+          <t>34→0</t>
         </is>
       </c>
     </row>
@@ -2154,23 +2154,23 @@
       </c>
       <c r="G49" s="14" t="inlineStr">
         <is>
-          <t>솔브레인홀딩스</t>
+          <t>하이록코리아</t>
         </is>
       </c>
       <c r="H49" s="15" t="n">
         <v>-14</v>
       </c>
       <c r="I49" s="15" t="n">
-        <v>-40162500</v>
+        <v>-35759500</v>
       </c>
       <c r="J49" s="16" t="inlineStr">
         <is>
-          <t>0.73%→0.60%</t>
+          <t>0.21%→0.10%</t>
         </is>
       </c>
       <c r="K49" s="13" t="inlineStr">
         <is>
-          <t>83→69</t>
+          <t>27→13</t>
         </is>
       </c>
     </row>
@@ -2198,23 +2198,23 @@
       </c>
       <c r="G50" s="14" t="inlineStr">
         <is>
-          <t>하이록코리아</t>
+          <t>솔브레인홀딩스</t>
         </is>
       </c>
       <c r="H50" s="15" t="n">
         <v>-14</v>
       </c>
       <c r="I50" s="15" t="n">
-        <v>-35759500</v>
+        <v>-40162500</v>
       </c>
       <c r="J50" s="16" t="inlineStr">
         <is>
-          <t>0.21%→0.10%</t>
+          <t>0.73%→0.60%</t>
         </is>
       </c>
       <c r="K50" s="13" t="inlineStr">
         <is>
-          <t>27→13</t>
+          <t>83→69</t>
         </is>
       </c>
     </row>

--- a/reports/pdf_rolling5_20260710.xlsx
+++ b/reports/pdf_rolling5_20260710.xlsx
@@ -574,7 +574,7 @@
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,448억      오늘 2026-07-10  vs  5일전 2026-07-03      매수 14종목  /  매도 15종목</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      오늘 2026-07-10  vs  5일전 2026-07-03      매수 14종목  /  매도 15종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -669,8 +669,10 @@
       <c r="B6" s="11" t="n">
         <v>109</v>
       </c>
-      <c r="C6" s="11" t="n">
-        <v>877815150</v>
+      <c r="C6" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
@@ -690,8 +692,10 @@
       <c r="H6" s="15" t="n">
         <v>-70</v>
       </c>
-      <c r="I6" s="15" t="n">
-        <v>-1026776800</v>
+      <c r="I6" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J6" s="16" t="inlineStr">
         <is>
@@ -713,8 +717,10 @@
       <c r="B7" s="11" t="n">
         <v>93</v>
       </c>
-      <c r="C7" s="11" t="n">
-        <v>970352700</v>
+      <c r="C7" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
@@ -734,8 +740,10 @@
       <c r="H7" s="15" t="n">
         <v>-54</v>
       </c>
-      <c r="I7" s="15" t="n">
-        <v>-818341920</v>
+      <c r="I7" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J7" s="16" t="inlineStr">
         <is>
@@ -757,8 +765,10 @@
       <c r="B8" s="11" t="n">
         <v>66</v>
       </c>
-      <c r="C8" s="11" t="n">
-        <v>2283200700</v>
+      <c r="C8" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
@@ -778,8 +788,10 @@
       <c r="H8" s="15" t="n">
         <v>-52</v>
       </c>
-      <c r="I8" s="15" t="n">
-        <v>-1464392800</v>
+      <c r="I8" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J8" s="16" t="inlineStr">
         <is>
@@ -801,8 +813,10 @@
       <c r="B9" s="11" t="n">
         <v>60</v>
       </c>
-      <c r="C9" s="11" t="n">
-        <v>4364004000</v>
+      <c r="C9" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
@@ -822,8 +836,10 @@
       <c r="H9" s="15" t="n">
         <v>-37</v>
       </c>
-      <c r="I9" s="15" t="n">
-        <v>-1169407200</v>
+      <c r="I9" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J9" s="16" t="inlineStr">
         <is>
@@ -845,8 +861,10 @@
       <c r="B10" s="11" t="n">
         <v>29</v>
       </c>
-      <c r="C10" s="11" t="n">
-        <v>1371905900</v>
+      <c r="C10" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
@@ -866,8 +884,10 @@
       <c r="H10" s="15" t="n">
         <v>-25</v>
       </c>
-      <c r="I10" s="15" t="n">
-        <v>-3672125000</v>
+      <c r="I10" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J10" s="16" t="inlineStr">
         <is>
@@ -889,8 +909,10 @@
       <c r="B11" s="11" t="n">
         <v>21</v>
       </c>
-      <c r="C11" s="11" t="n">
-        <v>1842241800</v>
+      <c r="C11" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
@@ -910,8 +932,10 @@
       <c r="H11" s="15" t="n">
         <v>-23</v>
       </c>
-      <c r="I11" s="15" t="n">
-        <v>-2444065100</v>
+      <c r="I11" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J11" s="16" t="inlineStr">
         <is>
@@ -933,8 +957,10 @@
       <c r="B12" s="11" t="n">
         <v>20</v>
       </c>
-      <c r="C12" s="11" t="n">
-        <v>1126456000</v>
+      <c r="C12" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
@@ -954,8 +980,10 @@
       <c r="H12" s="15" t="n">
         <v>-22</v>
       </c>
-      <c r="I12" s="15" t="n">
-        <v>-460205900</v>
+      <c r="I12" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J12" s="16" t="inlineStr">
         <is>
@@ -977,8 +1005,10 @@
       <c r="B13" s="11" t="n">
         <v>16</v>
       </c>
-      <c r="C13" s="11" t="n">
-        <v>1259361600</v>
+      <c r="C13" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
@@ -998,8 +1028,10 @@
       <c r="H13" s="15" t="n">
         <v>-20</v>
       </c>
-      <c r="I13" s="15" t="n">
-        <v>-844842000</v>
+      <c r="I13" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J13" s="16" t="inlineStr">
         <is>
@@ -1021,8 +1053,10 @@
       <c r="B14" s="11" t="n">
         <v>11</v>
       </c>
-      <c r="C14" s="11" t="n">
-        <v>430119800</v>
+      <c r="C14" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D14" s="12" t="inlineStr">
         <is>
@@ -1042,8 +1076,10 @@
       <c r="H14" s="15" t="n">
         <v>-19</v>
       </c>
-      <c r="I14" s="15" t="n">
-        <v>-1287624300</v>
+      <c r="I14" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J14" s="16" t="inlineStr">
         <is>
@@ -1065,8 +1101,10 @@
       <c r="B15" s="11" t="n">
         <v>10</v>
       </c>
-      <c r="C15" s="11" t="n">
-        <v>436603000</v>
+      <c r="C15" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
@@ -1086,8 +1124,10 @@
       <c r="H15" s="15" t="n">
         <v>-17</v>
       </c>
-      <c r="I15" s="15" t="n">
-        <v>-843829000</v>
+      <c r="I15" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J15" s="16" t="inlineStr">
         <is>
@@ -1109,8 +1149,10 @@
       <c r="B16" s="11" t="n">
         <v>10</v>
       </c>
-      <c r="C16" s="11" t="n">
-        <v>415836500</v>
+      <c r="C16" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D16" s="12" t="inlineStr">
         <is>
@@ -1130,8 +1172,10 @@
       <c r="H16" s="15" t="n">
         <v>-16</v>
       </c>
-      <c r="I16" s="15" t="n">
-        <v>-2466857600</v>
+      <c r="I16" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J16" s="16" t="inlineStr">
         <is>
@@ -1153,8 +1197,10 @@
       <c r="B17" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="C17" s="11" t="n">
-        <v>955461600</v>
+      <c r="C17" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
@@ -1174,8 +1220,10 @@
       <c r="H17" s="15" t="n">
         <v>-12</v>
       </c>
-      <c r="I17" s="15" t="n">
-        <v>-427891200</v>
+      <c r="I17" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J17" s="16" t="inlineStr">
         <is>
@@ -1191,23 +1239,25 @@
     <row r="18">
       <c r="A18" s="10" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>파마리서치</t>
         </is>
       </c>
       <c r="B18" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="C18" s="11" t="n">
-        <v>1519500000</v>
+      <c r="C18" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D18" s="12" t="inlineStr">
         <is>
-          <t>3.71%→3.93%</t>
+          <t>2.85%→3.13%</t>
         </is>
       </c>
       <c r="E18" s="13" t="inlineStr">
         <is>
-          <t>52→57</t>
+          <t>39→44</t>
         </is>
       </c>
       <c r="G18" s="14" t="inlineStr">
@@ -1218,8 +1268,10 @@
       <c r="H18" s="15" t="n">
         <v>-10</v>
       </c>
-      <c r="I18" s="15" t="n">
-        <v>-432551000</v>
+      <c r="I18" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J18" s="16" t="inlineStr">
         <is>
@@ -1235,23 +1287,25 @@
     <row r="19">
       <c r="A19" s="10" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="B19" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="C19" s="11" t="n">
-        <v>1565085000</v>
+      <c r="C19" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
-          <t>2.85%→3.13%</t>
+          <t>3.71%→3.93%</t>
         </is>
       </c>
       <c r="E19" s="13" t="inlineStr">
         <is>
-          <t>39→44</t>
+          <t>52→57</t>
         </is>
       </c>
       <c r="G19" s="14" t="inlineStr">
@@ -1262,8 +1316,10 @@
       <c r="H19" s="15" t="n">
         <v>-6</v>
       </c>
-      <c r="I19" s="15" t="n">
-        <v>-920817000</v>
+      <c r="I19" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J19" s="16" t="inlineStr">
         <is>
@@ -1290,8 +1346,10 @@
       <c r="H20" s="15" t="n">
         <v>-4</v>
       </c>
-      <c r="I20" s="15" t="n">
-        <v>-478946400</v>
+      <c r="I20" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J20" s="16" t="inlineStr">
         <is>
@@ -1307,7 +1365,7 @@
     <row r="22" ht="19" customHeight="1">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 4,303억      오늘 2026-07-10  vs  5일전 2026-07-03      매수 0종목  /  매도 0종목</t>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      오늘 2026-07-10  vs  5일전 2026-07-03      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B22" s="4" t="n"/>
@@ -1331,7 +1389,7 @@
     <row r="25" ht="19" customHeight="1">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,562억      오늘 2026-07-10  vs  5일전 2026-07-03      매수 4종목  /  매도 5종목</t>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      오늘 2026-07-10  vs  5일전 2026-07-03      매수 4종목  /  매도 5종목</t>
         </is>
       </c>
       <c r="B25" s="4" t="n"/>
@@ -1426,8 +1484,10 @@
       <c r="B28" s="11" t="n">
         <v>201</v>
       </c>
-      <c r="C28" s="11" t="n">
-        <v>5330158200</v>
+      <c r="C28" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D28" s="12" t="inlineStr">
         <is>
@@ -1447,8 +1507,10 @@
       <c r="H28" s="15" t="n">
         <v>-86</v>
       </c>
-      <c r="I28" s="15" t="n">
-        <v>-6197701800</v>
+      <c r="I28" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J28" s="16" t="inlineStr">
         <is>
@@ -1470,8 +1532,10 @@
       <c r="B29" s="11" t="n">
         <v>139</v>
       </c>
-      <c r="C29" s="11" t="n">
-        <v>6665411400</v>
+      <c r="C29" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D29" s="12" t="inlineStr">
         <is>
@@ -1491,8 +1555,10 @@
       <c r="H29" s="15" t="n">
         <v>-81</v>
       </c>
-      <c r="I29" s="15" t="n">
-        <v>-4323771900</v>
+      <c r="I29" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J29" s="16" t="inlineStr">
         <is>
@@ -1514,8 +1580,10 @@
       <c r="B30" s="11" t="n">
         <v>35</v>
       </c>
-      <c r="C30" s="11" t="n">
-        <v>7429905000</v>
+      <c r="C30" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D30" s="12" t="inlineStr">
         <is>
@@ -1535,8 +1603,10 @@
       <c r="H30" s="15" t="n">
         <v>-66</v>
       </c>
-      <c r="I30" s="15" t="n">
-        <v>-6574590000</v>
+      <c r="I30" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J30" s="16" t="inlineStr">
         <is>
@@ -1558,8 +1628,10 @@
       <c r="B31" s="11" t="n">
         <v>17</v>
       </c>
-      <c r="C31" s="11" t="n">
-        <v>1380457800</v>
+      <c r="C31" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D31" s="12" t="inlineStr">
         <is>
@@ -1579,8 +1651,10 @@
       <c r="H31" s="15" t="n">
         <v>-58</v>
       </c>
-      <c r="I31" s="15" t="n">
-        <v>-1402579200</v>
+      <c r="I31" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J31" s="16" t="inlineStr">
         <is>
@@ -1607,8 +1681,10 @@
       <c r="H32" s="15" t="n">
         <v>-40</v>
       </c>
-      <c r="I32" s="15" t="n">
-        <v>-4163220000</v>
+      <c r="I32" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J32" s="16" t="inlineStr">
         <is>
@@ -1624,7 +1700,7 @@
     <row r="34" ht="19" customHeight="1">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,548억      오늘 2026-07-10  vs  5일전 2026-07-03      매수 0종목  /  매도 0종목</t>
+          <t>■ TIME K바이오액티브  (타임폴리오)      오늘 2026-07-10  vs  5일전 2026-07-03      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B34" s="4" t="n"/>
@@ -1648,7 +1724,7 @@
     <row r="37" ht="19" customHeight="1">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 329억      오늘 2026-07-10  vs  5일전 2026-07-03      매수 15종목  /  매도 15종목</t>
+          <t>■ PLUS 코스닥150액티브  (한화)      오늘 2026-07-10  vs  5일전 2026-07-03      매수 15종목  /  매도 15종목</t>
         </is>
       </c>
       <c r="B37" s="4" t="n"/>
@@ -1743,12 +1819,14 @@
       <c r="B40" s="11" t="n">
         <v>121</v>
       </c>
-      <c r="C40" s="11" t="n">
-        <v>87833900</v>
+      <c r="C40" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D40" s="12" t="inlineStr">
         <is>
-          <t>6.71%→6.95%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E40" s="13" t="inlineStr">
@@ -1764,12 +1842,14 @@
       <c r="H40" s="15" t="n">
         <v>-318</v>
       </c>
-      <c r="I40" s="15" t="n">
-        <v>-100551600</v>
+      <c r="I40" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J40" s="16" t="inlineStr">
         <is>
-          <t>2.96%→2.64%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K40" s="13" t="inlineStr">
@@ -1787,12 +1867,14 @@
       <c r="B41" s="11" t="n">
         <v>91</v>
       </c>
-      <c r="C41" s="11" t="n">
-        <v>21541975</v>
+      <c r="C41" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D41" s="12" t="inlineStr">
         <is>
-          <t>0.37%→0.43%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E41" s="13" t="inlineStr">
@@ -1808,12 +1890,14 @@
       <c r="H41" s="15" t="n">
         <v>-192</v>
       </c>
-      <c r="I41" s="15" t="n">
-        <v>-105590400</v>
+      <c r="I41" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J41" s="16" t="inlineStr">
         <is>
-          <t>0.63%→0.31%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K41" s="13" t="inlineStr">
@@ -1831,12 +1915,14 @@
       <c r="B42" s="11" t="n">
         <v>37</v>
       </c>
-      <c r="C42" s="11" t="n">
-        <v>109603250</v>
+      <c r="C42" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D42" s="12" t="inlineStr">
         <is>
-          <t>0.00%→0.33%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E42" s="13" t="inlineStr">
@@ -1846,23 +1932,25 @@
       </c>
       <c r="G42" s="14" t="inlineStr">
         <is>
-          <t>서부T&amp;D</t>
+          <t>씨어스</t>
         </is>
       </c>
       <c r="H42" s="15" t="n">
         <v>-36</v>
       </c>
-      <c r="I42" s="15" t="n">
-        <v>-31518000</v>
+      <c r="I42" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J42" s="16" t="inlineStr">
         <is>
-          <t>0.20%→0.10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K42" s="13" t="inlineStr">
         <is>
-          <t>73→37</t>
+          <t>733→697</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1963,14 @@
       <c r="B43" s="11" t="n">
         <v>30</v>
       </c>
-      <c r="C43" s="11" t="n">
-        <v>98430000</v>
+      <c r="C43" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D43" s="12" t="inlineStr">
         <is>
-          <t>2.11%→2.40%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E43" s="13" t="inlineStr">
@@ -1890,23 +1980,25 @@
       </c>
       <c r="G43" s="14" t="inlineStr">
         <is>
-          <t>씨어스</t>
+          <t>서부T&amp;D</t>
         </is>
       </c>
       <c r="H43" s="15" t="n">
         <v>-36</v>
       </c>
-      <c r="I43" s="15" t="n">
-        <v>-99450000</v>
+      <c r="I43" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J43" s="16" t="inlineStr">
         <is>
-          <t>6.20%→5.87%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K43" s="13" t="inlineStr">
         <is>
-          <t>733→697</t>
+          <t>73→37</t>
         </is>
       </c>
     </row>
@@ -1919,12 +2011,14 @@
       <c r="B44" s="11" t="n">
         <v>16</v>
       </c>
-      <c r="C44" s="11" t="n">
-        <v>197200000</v>
+      <c r="C44" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D44" s="12" t="inlineStr">
         <is>
-          <t>2.72%→3.30%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E44" s="13" t="inlineStr">
@@ -1940,12 +2034,14 @@
       <c r="H44" s="15" t="n">
         <v>-34</v>
       </c>
-      <c r="I44" s="15" t="n">
-        <v>-31501000</v>
+      <c r="I44" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J44" s="16" t="inlineStr">
         <is>
-          <t>0.23%→0.14%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K44" s="13" t="inlineStr">
@@ -1963,12 +2059,14 @@
       <c r="B45" s="11" t="n">
         <v>13</v>
       </c>
-      <c r="C45" s="11" t="n">
-        <v>95693000</v>
+      <c r="C45" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D45" s="12" t="inlineStr">
         <is>
-          <t>3.38%→3.66%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E45" s="13" t="inlineStr">
@@ -1984,12 +2082,14 @@
       <c r="H45" s="15" t="n">
         <v>-34</v>
       </c>
-      <c r="I45" s="15" t="n">
-        <v>-16010600</v>
+      <c r="I45" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J45" s="16" t="inlineStr">
         <is>
-          <t>0.05%→0.00%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K45" s="13" t="inlineStr">
@@ -2007,12 +2107,14 @@
       <c r="B46" s="11" t="n">
         <v>12</v>
       </c>
-      <c r="C46" s="11" t="n">
-        <v>106998000</v>
+      <c r="C46" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D46" s="12" t="inlineStr">
         <is>
-          <t>2.32%→2.63%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E46" s="13" t="inlineStr">
@@ -2028,12 +2130,14 @@
       <c r="H46" s="15" t="n">
         <v>-31</v>
       </c>
-      <c r="I46" s="15" t="n">
-        <v>-46165200</v>
+      <c r="I46" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J46" s="16" t="inlineStr">
         <is>
-          <t>0.34%→0.20%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K46" s="13" t="inlineStr">
@@ -2051,12 +2155,14 @@
       <c r="B47" s="11" t="n">
         <v>12</v>
       </c>
-      <c r="C47" s="11" t="n">
-        <v>155244000</v>
+      <c r="C47" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D47" s="12" t="inlineStr">
         <is>
-          <t>2.38%→2.84%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E47" s="13" t="inlineStr">
@@ -2072,12 +2178,14 @@
       <c r="H47" s="15" t="n">
         <v>-27</v>
       </c>
-      <c r="I47" s="15" t="n">
-        <v>-77571000</v>
+      <c r="I47" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J47" s="16" t="inlineStr">
         <is>
-          <t>0.24%→0.00%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K47" s="13" t="inlineStr">
@@ -2089,23 +2197,25 @@
     <row r="48">
       <c r="A48" s="10" t="inlineStr">
         <is>
-          <t>HPSP</t>
+          <t>코미코</t>
         </is>
       </c>
       <c r="B48" s="11" t="n">
         <v>10</v>
       </c>
-      <c r="C48" s="11" t="n">
-        <v>33405000</v>
+      <c r="C48" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D48" s="12" t="inlineStr">
         <is>
-          <t>1.17%→1.26%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E48" s="13" t="inlineStr">
         <is>
-          <t>114→124</t>
+          <t>142→152</t>
         </is>
       </c>
       <c r="G48" s="14" t="inlineStr">
@@ -2116,12 +2226,14 @@
       <c r="H48" s="15" t="n">
         <v>-16</v>
       </c>
-      <c r="I48" s="15" t="n">
-        <v>-48348000</v>
+      <c r="I48" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J48" s="16" t="inlineStr">
         <is>
-          <t>0.79%→0.64%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K48" s="13" t="inlineStr">
@@ -2133,23 +2245,25 @@
     <row r="49">
       <c r="A49" s="10" t="inlineStr">
         <is>
-          <t>코미코</t>
+          <t>HPSP</t>
         </is>
       </c>
       <c r="B49" s="11" t="n">
         <v>10</v>
       </c>
-      <c r="C49" s="11" t="n">
-        <v>64515000</v>
+      <c r="C49" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D49" s="12" t="inlineStr">
         <is>
-          <t>2.80%→2.99%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E49" s="13" t="inlineStr">
         <is>
-          <t>142→152</t>
+          <t>114→124</t>
         </is>
       </c>
       <c r="G49" s="14" t="inlineStr">
@@ -2160,12 +2274,14 @@
       <c r="H49" s="15" t="n">
         <v>-14</v>
       </c>
-      <c r="I49" s="15" t="n">
-        <v>-35759500</v>
+      <c r="I49" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J49" s="16" t="inlineStr">
         <is>
-          <t>0.21%→0.10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K49" s="13" t="inlineStr">
@@ -2183,12 +2299,14 @@
       <c r="B50" s="11" t="n">
         <v>6</v>
       </c>
-      <c r="C50" s="11" t="n">
-        <v>38046000</v>
+      <c r="C50" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D50" s="12" t="inlineStr">
         <is>
-          <t>1.42%→1.53%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E50" s="13" t="inlineStr">
@@ -2204,12 +2322,14 @@
       <c r="H50" s="15" t="n">
         <v>-14</v>
       </c>
-      <c r="I50" s="15" t="n">
-        <v>-40162500</v>
+      <c r="I50" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J50" s="16" t="inlineStr">
         <is>
-          <t>0.73%→0.60%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K50" s="13" t="inlineStr">
@@ -2227,12 +2347,14 @@
       <c r="B51" s="11" t="n">
         <v>6</v>
       </c>
-      <c r="C51" s="11" t="n">
-        <v>38709000</v>
+      <c r="C51" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D51" s="12" t="inlineStr">
         <is>
-          <t>0.91%→1.02%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E51" s="13" t="inlineStr">
@@ -2248,12 +2370,14 @@
       <c r="H51" s="15" t="n">
         <v>-13</v>
       </c>
-      <c r="I51" s="15" t="n">
-        <v>-100223500</v>
+      <c r="I51" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J51" s="16" t="inlineStr">
         <is>
-          <t>2.31%→2.00%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K51" s="13" t="inlineStr">
@@ -2271,12 +2395,14 @@
       <c r="B52" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="C52" s="11" t="n">
-        <v>17722500</v>
+      <c r="C52" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D52" s="12" t="inlineStr">
         <is>
-          <t>6.83%→6.85%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E52" s="13" t="inlineStr">
@@ -2292,12 +2418,14 @@
       <c r="H52" s="15" t="n">
         <v>-10</v>
       </c>
-      <c r="I52" s="15" t="n">
-        <v>-73610000</v>
+      <c r="I52" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J52" s="16" t="inlineStr">
         <is>
-          <t>1.08%→0.85%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K52" s="13" t="inlineStr">
@@ -2315,12 +2443,14 @@
       <c r="B53" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="C53" s="11" t="n">
-        <v>36337500</v>
+      <c r="C53" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D53" s="12" t="inlineStr">
         <is>
-          <t>0.00%→0.11%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E53" s="13" t="inlineStr">
@@ -2336,12 +2466,14 @@
       <c r="H53" s="15" t="n">
         <v>-7</v>
       </c>
-      <c r="I53" s="15" t="n">
-        <v>-68544000</v>
+      <c r="I53" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J53" s="16" t="inlineStr">
         <is>
-          <t>3.21%→2.98%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K53" s="13" t="inlineStr">
@@ -2359,12 +2491,14 @@
       <c r="B54" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="C54" s="11" t="n">
-        <v>57630000</v>
+      <c r="C54" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D54" s="12" t="inlineStr">
         <is>
-          <t>2.59%→2.75%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E54" s="13" t="inlineStr">
@@ -2380,12 +2514,14 @@
       <c r="H54" s="15" t="n">
         <v>-3</v>
       </c>
-      <c r="I54" s="15" t="n">
-        <v>-73567500</v>
+      <c r="I54" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J54" s="16" t="inlineStr">
         <is>
-          <t>2.03%→1.79%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K54" s="13" t="inlineStr">
@@ -2397,7 +2533,7 @@
     <row r="56" ht="19" customHeight="1">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 568억      오늘 2026-07-10  vs  5일전 2026-07-03      매수 6종목  /  매도 4종목</t>
+          <t>■ RISE 바이오TOP10액티브  (KB)      오늘 2026-07-10  vs  5일전 2026-07-03      매수 6종목  /  매도 4종목</t>
         </is>
       </c>
       <c r="B56" s="4" t="n"/>
@@ -2492,8 +2628,10 @@
       <c r="B59" s="11" t="n">
         <v>297</v>
       </c>
-      <c r="C59" s="11" t="n">
-        <v>848113200</v>
+      <c r="C59" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D59" s="12" t="inlineStr">
         <is>
@@ -2513,8 +2651,10 @@
       <c r="H59" s="15" t="n">
         <v>-685</v>
       </c>
-      <c r="I59" s="15" t="n">
-        <v>-751719000</v>
+      <c r="I59" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J59" s="16" t="inlineStr">
         <is>
@@ -2536,8 +2676,10 @@
       <c r="B60" s="11" t="n">
         <v>77</v>
       </c>
-      <c r="C60" s="11" t="n">
-        <v>123569600</v>
+      <c r="C60" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D60" s="12" t="inlineStr">
         <is>
@@ -2557,8 +2699,10 @@
       <c r="H60" s="15" t="n">
         <v>-122</v>
       </c>
-      <c r="I60" s="15" t="n">
-        <v>-1747674400</v>
+      <c r="I60" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J60" s="16" t="inlineStr">
         <is>
@@ -2580,8 +2724,10 @@
       <c r="B61" s="11" t="n">
         <v>35</v>
       </c>
-      <c r="C61" s="11" t="n">
-        <v>714903000</v>
+      <c r="C61" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D61" s="12" t="inlineStr">
         <is>
@@ -2601,8 +2747,10 @@
       <c r="H61" s="15" t="n">
         <v>-36</v>
       </c>
-      <c r="I61" s="15" t="n">
-        <v>-502113600</v>
+      <c r="I61" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J61" s="16" t="inlineStr">
         <is>
@@ -2624,8 +2772,10 @@
       <c r="B62" s="11" t="n">
         <v>16</v>
       </c>
-      <c r="C62" s="11" t="n">
-        <v>757088000</v>
+      <c r="C62" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D62" s="12" t="inlineStr">
         <is>
@@ -2645,8 +2795,10 @@
       <c r="H62" s="15" t="n">
         <v>-13</v>
       </c>
-      <c r="I62" s="15" t="n">
-        <v>-460200000</v>
+      <c r="I62" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J62" s="16" t="inlineStr">
         <is>
@@ -2668,8 +2820,10 @@
       <c r="B63" s="11" t="n">
         <v>14</v>
       </c>
-      <c r="C63" s="11" t="n">
-        <v>510468000</v>
+      <c r="C63" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D63" s="12" t="inlineStr">
         <is>
@@ -2696,8 +2850,10 @@
       <c r="B64" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="C64" s="11" t="n">
-        <v>37996000</v>
+      <c r="C64" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D64" s="12" t="inlineStr">
         <is>
